--- a/artfynd/A 11868-2026 artfynd.xlsx
+++ b/artfynd/A 11868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1211971</v>
+        <v>548030</v>
       </c>
       <c r="B2" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4363</v>
+        <v>2058</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577137.6778497042</v>
+        <v>576998</v>
       </c>
       <c r="R2" t="n">
-        <v>6711125.989643759</v>
+        <v>6711020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>blandskog</t>
+          <t>gammal granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,52 +786,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7042069</v>
+        <v>548031</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vingesbacke, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090.018625072</v>
+        <v>577053</v>
       </c>
       <c r="R3" t="n">
-        <v>6711094.443792205</v>
+        <v>6711003</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-11-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,9 +874,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gammal granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,6 +894,822 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111755971</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91361</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577035</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6711054</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7042069</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vingesbacke, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577090</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6711094</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-11-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-11-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1211971</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93193</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vingesbacke, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577138</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6711126</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-09-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-09-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1326188</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vingesbacke, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577083</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6711129</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lena Melin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111755945</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577114</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6711161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111755946</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577063</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6711100</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111755969</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576993</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6711023</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111755953</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storberget, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577070</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6711097</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11868-2026 artfynd.xlsx
+++ b/artfynd/A 11868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/548030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/548031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7042069</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1211971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1326188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755945</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755946</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755969</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,8 +1760,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111755953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>